--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>282</v>
+        <v>373</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>274</v>
+        <v>416</v>
       </c>
       <c r="E3">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -450,7 +450,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>416</v>
@@ -459,7 +459,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
